--- a/tinHelm/excel/Card.xlsx
+++ b/tinHelm/excel/Card.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -43,6 +43,15 @@
     <t>卡牌描述</t>
   </si>
   <si>
+    <t>骰子点数触发条件</t>
+  </si>
+  <si>
+    <t>骰子Icon触发条件</t>
+  </si>
+  <si>
+    <t>骰子点数触发条件描述</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -52,12 +61,21 @@
     <t>des</t>
   </si>
   <si>
+    <t>numNeed</t>
+  </si>
+  <si>
+    <t>DiceNeed</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>array</t>
+  </si>
+  <si>
     <t>server</t>
   </si>
   <si>
@@ -70,16 +88,61 @@
     <t>进行一次防御</t>
   </si>
   <si>
+    <t>["double"]</t>
+  </si>
+  <si>
+    <t>[6001,6002]</t>
+  </si>
+  <si>
+    <t>需要两枚点数一样的骰子</t>
+  </si>
+  <si>
     <t>技巧</t>
   </si>
   <si>
     <t>发动一次技巧</t>
   </si>
   <si>
+    <t>["littleStraight"]</t>
+  </si>
+  <si>
+    <t>[6001,6003]</t>
+  </si>
+  <si>
+    <t>大顺子（1-5）</t>
+  </si>
+  <si>
     <t>攻击</t>
   </si>
   <si>
     <t>进行一次攻击</t>
+  </si>
+  <si>
+    <t>["bigStraight"]</t>
+  </si>
+  <si>
+    <t>[6001,6004]</t>
+  </si>
+  <si>
+    <t>小顺子（1-4 or 2-5）</t>
+  </si>
+  <si>
+    <t>[6005,6005]</t>
+  </si>
+  <si>
+    <t>[6005,6006]</t>
+  </si>
+  <si>
+    <t>[6005,6007]</t>
+  </si>
+  <si>
+    <t>[60011,6008]</t>
+  </si>
+  <si>
+    <t>[60011,6009]</t>
+  </si>
+  <si>
+    <t>[60012,6010]</t>
   </si>
 </sst>
 </file>
@@ -1016,6 +1079,9 @@
   <cols>
     <col min="1" max="1" width="15.5916666666667" customWidth="1"/>
     <col min="3" max="3" width="13.3583333333333" customWidth="1"/>
+    <col min="4" max="4" width="23.3583333333333" customWidth="1"/>
+    <col min="5" max="5" width="15.0916666666667" customWidth="1"/>
+    <col min="6" max="6" width="20.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1028,69 +1094,99 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7">
@@ -1098,14 +1194,20 @@
         <v>2001</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:7">
@@ -1113,14 +1215,20 @@
         <v>2002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7">
@@ -1128,14 +1236,20 @@
         <v>2003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7">
@@ -1143,10 +1257,19 @@
         <v>2004</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1154,10 +1277,19 @@
         <v>2005</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1165,10 +1297,19 @@
         <v>2006</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1176,10 +1317,19 @@
         <v>2007</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1187,10 +1337,19 @@
         <v>2008</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1198,10 +1357,19 @@
         <v>2009</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/tinHelm/excel/Card.xlsx
+++ b/tinHelm/excel/Card.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="29790" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="38">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>DiceNeed</t>
+  </si>
+  <si>
+    <t>numNeedDes</t>
   </si>
   <si>
     <t>int</t>
@@ -1122,25 +1125,25 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -1149,43 +1152,43 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -1194,19 +1197,19 @@
         <v>2001</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1"/>
     </row>
@@ -1215,19 +1218,19 @@
         <v>2002</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1"/>
     </row>
@@ -1236,19 +1239,19 @@
         <v>2003</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1"/>
     </row>
@@ -1257,19 +1260,19 @@
         <v>2004</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1277,19 +1280,19 @@
         <v>2005</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1297,19 +1300,19 @@
         <v>2006</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1317,19 +1320,19 @@
         <v>2007</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1337,19 +1340,19 @@
         <v>2008</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1357,19 +1360,19 @@
         <v>2009</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/tinHelm/excel/Card.xlsx
+++ b/tinHelm/excel/Card.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29790" windowHeight="10455"/>
+    <workbookView windowWidth="17895" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/tinHelm/excel/Card.xlsx
+++ b/tinHelm/excel/Card.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17895" windowHeight="8220"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>["double"]</t>
   </si>
   <si>
-    <t>[6001,6002]</t>
+    <t>[1,2]</t>
   </si>
   <si>
     <t>需要两枚点数一样的骰子</t>
@@ -109,7 +109,7 @@
     <t>["littleStraight"]</t>
   </si>
   <si>
-    <t>[6001,6003]</t>
+    <t>[1,3]</t>
   </si>
   <si>
     <t>大顺子（1-5）</t>
@@ -124,28 +124,28 @@
     <t>["bigStraight"]</t>
   </si>
   <si>
-    <t>[6001,6004]</t>
+    <t>[1,4]</t>
   </si>
   <si>
     <t>小顺子（1-4 or 2-5）</t>
   </si>
   <si>
-    <t>[6005,6005]</t>
-  </si>
-  <si>
-    <t>[6005,6006]</t>
-  </si>
-  <si>
-    <t>[6005,6007]</t>
-  </si>
-  <si>
-    <t>[60011,6008]</t>
-  </si>
-  <si>
-    <t>[60011,6009]</t>
-  </si>
-  <si>
-    <t>[60012,6010]</t>
+    <t>[5,5]</t>
+  </si>
+  <si>
+    <t>[5,6]</t>
+  </si>
+  <si>
+    <t>[5,7]</t>
+  </si>
+  <si>
+    <t>[11,8]</t>
+  </si>
+  <si>
+    <t>[11,9]</t>
+  </si>
+  <si>
+    <t>[12,10]</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1">
-        <v>2001</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>17</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1">
-        <v>2002</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>22</v>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1">
-        <v>2003</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>27</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1">
-        <v>2004</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>17</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1">
-        <v>2005</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1">
-        <v>2006</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>27</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1">
-        <v>2007</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>17</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
-        <v>2008</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>22</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
-        <v>2009</v>
+        <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>27</v>
